--- a/مصاريف الأشهر.xlsx
+++ b/مصاريف الأشهر.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{145643CD-8DDC-084D-BC4B-DDC3BC5E3C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7C79D9-A812-7143-B87C-C4608D288BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="27240" windowHeight="16180" xr2:uid="{3B47F104-2E91-B745-9A15-2E71BAAB6C79}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" activeTab="1" xr2:uid="{3B47F104-2E91-B745-9A15-2E71BAAB6C79}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="114">
   <si>
     <t>يناير</t>
   </si>
@@ -207,6 +211,177 @@
   </si>
   <si>
     <t>مارس</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>مهم ومستعجل</t>
+  </si>
+  <si>
+    <t>مهم غيرمستعجل</t>
+  </si>
+  <si>
+    <t>غير مهم وغيرمستعجل</t>
+  </si>
+  <si>
+    <t>المصروف</t>
+  </si>
+  <si>
+    <t>المبلغ</t>
+  </si>
+  <si>
+    <t>الشهر</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>21 Total</t>
+  </si>
+  <si>
+    <t>34 Total</t>
+  </si>
+  <si>
+    <t>36 Total</t>
+  </si>
+  <si>
+    <t>39 Total</t>
+  </si>
+  <si>
+    <t>50 Total</t>
+  </si>
+  <si>
+    <t>52 Total</t>
+  </si>
+  <si>
+    <t>60 Total</t>
+  </si>
+  <si>
+    <t>64 Total</t>
+  </si>
+  <si>
+    <t>70 Total</t>
+  </si>
+  <si>
+    <t>100 Total</t>
+  </si>
+  <si>
+    <t>101 Total</t>
+  </si>
+  <si>
+    <t>108 Total</t>
+  </si>
+  <si>
+    <t>141 Total</t>
+  </si>
+  <si>
+    <t>150 Total</t>
+  </si>
+  <si>
+    <t>151 Total</t>
+  </si>
+  <si>
+    <t>154 Total</t>
+  </si>
+  <si>
+    <t>168 Total</t>
+  </si>
+  <si>
+    <t>170 Total</t>
+  </si>
+  <si>
+    <t>200 Total</t>
+  </si>
+  <si>
+    <t>233 Total</t>
+  </si>
+  <si>
+    <t>235 Total</t>
+  </si>
+  <si>
+    <t>239 Total</t>
+  </si>
+  <si>
+    <t>276 Total</t>
+  </si>
+  <si>
+    <t>286 Total</t>
+  </si>
+  <si>
+    <t>300 Total</t>
+  </si>
+  <si>
+    <t>325 Total</t>
+  </si>
+  <si>
+    <t>339 Total</t>
+  </si>
+  <si>
+    <t>345 Total</t>
+  </si>
+  <si>
+    <t>349 Total</t>
+  </si>
+  <si>
+    <t>350 Total</t>
+  </si>
+  <si>
+    <t>400 Total</t>
+  </si>
+  <si>
+    <t>407 Total</t>
+  </si>
+  <si>
+    <t>430 Total</t>
+  </si>
+  <si>
+    <t>479 Total</t>
+  </si>
+  <si>
+    <t>512 Total</t>
+  </si>
+  <si>
+    <t>531 Total</t>
+  </si>
+  <si>
+    <t>562 Total</t>
+  </si>
+  <si>
+    <t>597 Total</t>
+  </si>
+  <si>
+    <t>836 Total</t>
+  </si>
+  <si>
+    <t>963 Total</t>
+  </si>
+  <si>
+    <t>1000 Total</t>
+  </si>
+  <si>
+    <t>1200 Total</t>
+  </si>
+  <si>
+    <t>1600 Total</t>
+  </si>
+  <si>
+    <t>1800 Total</t>
+  </si>
+  <si>
+    <t>2000 Total</t>
   </si>
 </sst>
 </file>
@@ -249,10 +424,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -268,6 +453,1251 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ahmad Abutalib" refreshedDate="46108.895294444446" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="65" xr:uid="{0542A349-8430-FE44-A72C-78DA00BAD747}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F66" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="الشهر" numFmtId="0">
+      <sharedItems count="3">
+        <s v="يناير"/>
+        <s v="فبراير"/>
+        <s v="مارس"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="المصروف" numFmtId="0">
+      <sharedItems count="54">
+        <s v="مستشفى"/>
+        <s v="اشتراك ايمن"/>
+        <s v="مصروف"/>
+        <s v="ملابس"/>
+        <s v="شاليه"/>
+        <s v="استراحة"/>
+        <s v="دروس خصوصية"/>
+        <s v="دواء عمتي"/>
+        <s v="جاكيت"/>
+        <s v="جزمة منى"/>
+        <s v="سكتشر2"/>
+        <s v="سكيتشر"/>
+        <s v="جمعية"/>
+        <s v="أدوية "/>
+        <s v="كيتا"/>
+        <s v="عباية"/>
+        <s v="كتاب وبخاخ"/>
+        <s v="بندة"/>
+        <s v="المزرعة"/>
+        <s v="غدا وحلا"/>
+        <s v="لحم"/>
+        <s v="ستارة ومكسرات"/>
+        <s v="ثياب"/>
+        <s v="لصق الخشم"/>
+        <s v="ملابس منى"/>
+        <s v="العجيمي"/>
+        <s v="جلابية لمنى"/>
+        <s v="مساج علاجي"/>
+        <s v="تغيير زيت"/>
+        <s v="فحوصات"/>
+        <s v="كتاب"/>
+        <s v="مساج"/>
+        <s v="فاتورة كهرباء أهلي"/>
+        <s v="علاج إرشاد النفسي"/>
+        <s v="غدا للبيت"/>
+        <s v="نابستر للجامعة"/>
+        <s v="حزام"/>
+        <s v="دراجة هوائية"/>
+        <s v="لصق للخشم"/>
+        <s v="تأجيل مادة b207b"/>
+        <s v="لصق خشم"/>
+        <s v="تصليح الماك"/>
+        <s v="حلاقة ومصاريف عيد"/>
+        <s v="صدقات"/>
+        <s v="طلعة هشام"/>
+        <s v="عطر وسحور"/>
+        <s v="علاج إرشاد"/>
+        <s v="عيدية منى"/>
+        <s v="غدا العيد"/>
+        <s v="قسط كنبة"/>
+        <s v="ملابس صيف"/>
+        <s v="ألعاب أطفال للعيد"/>
+        <s v="شغالة باليوم"/>
+        <s v="تجديد جواز منى"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="المبلغ" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="21" maxValue="2000" count="45">
+        <n v="151"/>
+        <n v="150"/>
+        <n v="400"/>
+        <n v="200"/>
+        <n v="325"/>
+        <n v="1000"/>
+        <n v="170"/>
+        <n v="300"/>
+        <n v="239"/>
+        <n v="479"/>
+        <n v="339"/>
+        <n v="349"/>
+        <n v="2000"/>
+        <n v="286"/>
+        <n v="21"/>
+        <n v="39"/>
+        <n v="407"/>
+        <n v="154"/>
+        <n v="141"/>
+        <n v="233"/>
+        <n v="52"/>
+        <n v="34"/>
+        <n v="60"/>
+        <n v="1600"/>
+        <n v="836"/>
+        <n v="963"/>
+        <n v="168"/>
+        <n v="100"/>
+        <n v="70"/>
+        <n v="235"/>
+        <n v="350"/>
+        <n v="597"/>
+        <n v="50"/>
+        <n v="36"/>
+        <n v="512"/>
+        <n v="108"/>
+        <n v="562"/>
+        <n v="64"/>
+        <n v="531"/>
+        <n v="1800"/>
+        <n v="276"/>
+        <n v="345"/>
+        <n v="1200"/>
+        <n v="101"/>
+        <n v="430"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="مهم ومستعجل" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <s v="نعم"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="مهم غيرمستعجل" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="نعم"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="غير مهم وغيرمستعجل" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="نعم"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="65">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="19"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="24"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="25"/>
+    <x v="25"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="26"/>
+    <x v="26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="28"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="29"/>
+    <x v="27"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="30"/>
+    <x v="28"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="27"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="31"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="32"/>
+    <x v="29"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="33"/>
+    <x v="30"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="34"/>
+    <x v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="35"/>
+    <x v="32"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="36"/>
+    <x v="33"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="37"/>
+    <x v="34"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="38"/>
+    <x v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="39"/>
+    <x v="36"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="40"/>
+    <x v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="41"/>
+    <x v="23"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="38"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="42"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="43"/>
+    <x v="39"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="44"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="45"/>
+    <x v="40"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="46"/>
+    <x v="41"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="47"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="48"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="49"/>
+    <x v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="42"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="50"/>
+    <x v="30"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="51"/>
+    <x v="37"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="52"/>
+    <x v="43"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="53"/>
+    <x v="44"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C07698F1-37EC-0B41-AE6D-05CC876C349D}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:DE16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="55">
+        <item x="13"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="51"/>
+        <item x="25"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="39"/>
+        <item x="53"/>
+        <item x="41"/>
+        <item x="28"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="36"/>
+        <item x="42"/>
+        <item x="37"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="4"/>
+        <item x="52"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="15"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="33"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="34"/>
+        <item x="19"/>
+        <item x="32"/>
+        <item x="29"/>
+        <item x="49"/>
+        <item x="30"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="40"/>
+        <item x="38"/>
+        <item x="31"/>
+        <item x="27"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="50"/>
+        <item x="24"/>
+        <item x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="46">
+        <item x="14"/>
+        <item x="21"/>
+        <item x="33"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="37"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="43"/>
+        <item x="35"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="19"/>
+        <item x="29"/>
+        <item x="8"/>
+        <item x="40"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item x="41"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="44"/>
+        <item x="9"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="36"/>
+        <item x="31"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="42"/>
+        <item x="23"/>
+        <item x="39"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="3"/>
+    <field x="4"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="2"/>
+    <field x="1"/>
+  </colFields>
+  <colItems count="108">
+    <i>
+      <x/>
+      <x v="49"/>
+    </i>
+    <i t="default">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="5"/>
+    </i>
+    <i t="default">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="16"/>
+    </i>
+    <i t="default">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="41"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="53"/>
+    </i>
+    <i t="default">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x v="41"/>
+    </i>
+    <i t="default">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x v="42"/>
+    </i>
+    <i t="default">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i t="default">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x v="39"/>
+    </i>
+    <i t="default">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i t="default">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x v="25"/>
+    </i>
+    <i t="default">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x v="45"/>
+    </i>
+    <i t="default">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+      <x v="6"/>
+    </i>
+    <i t="default">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i t="default">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+      <x v="48"/>
+    </i>
+    <i t="default">
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+      <x v="40"/>
+    </i>
+    <i t="default">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+      <x v="14"/>
+    </i>
+    <i t="default">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+      <x v="19"/>
+    </i>
+    <i t="default">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+    </i>
+    <i t="default">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+      <x v="28"/>
+    </i>
+    <i t="default">
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+      <x v="36"/>
+    </i>
+    <i t="default">
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+      <x v="12"/>
+    </i>
+    <i t="default">
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+      <x v="29"/>
+    </i>
+    <i t="default">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+      <x/>
+    </i>
+    <i t="default">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i t="default">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+      <x v="24"/>
+    </i>
+    <i t="default">
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+      <x v="22"/>
+    </i>
+    <i t="default">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+      <x v="30"/>
+    </i>
+    <i t="default">
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+      <x v="23"/>
+    </i>
+    <i t="default">
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i t="default">
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i t="default">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+      <x v="28"/>
+    </i>
+    <i t="default">
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+      <x v="8"/>
+    </i>
+    <i t="default">
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+      <x v="13"/>
+    </i>
+    <i t="default">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+      <x v="18"/>
+    </i>
+    <i t="default">
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+      <x v="11"/>
+    </i>
+    <i t="default">
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+      <x v="7"/>
+    </i>
+    <i t="default">
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+      <x v="34"/>
+    </i>
+    <i t="default">
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+      <x v="52"/>
+    </i>
+    <i t="default">
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+      <x v="4"/>
+    </i>
+    <i t="default">
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="default">
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+      <x v="49"/>
+    </i>
+    <i t="default">
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i t="default">
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+      <x v="26"/>
+    </i>
+    <i t="default">
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+      <x v="15"/>
+    </i>
+    <i t="default">
+      <x v="44"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,10 +2016,685 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F5ABA7E-EDE7-394F-8F7D-1313153AB597}">
+  <dimension ref="A1:DE16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="67" max="69" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="10" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="92" max="94" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="101" max="102" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="19" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="15.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4">
+        <v>60</v>
+      </c>
+      <c r="O4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4">
+        <v>70</v>
+      </c>
+      <c r="T4" t="s">
+        <v>77</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="W4" t="s">
+        <v>78</v>
+      </c>
+      <c r="X4">
+        <v>101</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z4">
+        <v>108</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB4">
+        <v>141</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD4">
+        <v>150</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG4">
+        <v>151</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI4">
+        <v>154</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK4">
+        <v>168</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO4">
+        <v>200</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU4">
+        <v>233</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW4">
+        <v>235</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AY4">
+        <v>239</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA4">
+        <v>276</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC4">
+        <v>286</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE4">
+        <v>300</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BL4">
+        <v>325</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BN4">
+        <v>339</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BP4">
+        <v>345</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BR4">
+        <v>349</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BT4">
+        <v>350</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX4">
+        <v>400</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA4">
+        <v>407</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>100</v>
+      </c>
+      <c r="CC4">
+        <v>430</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE4">
+        <v>479</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>102</v>
+      </c>
+      <c r="CG4">
+        <v>512</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>103</v>
+      </c>
+      <c r="CI4">
+        <v>531</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>104</v>
+      </c>
+      <c r="CK4">
+        <v>562</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>105</v>
+      </c>
+      <c r="CM4">
+        <v>597</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>106</v>
+      </c>
+      <c r="CO4">
+        <v>836</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>107</v>
+      </c>
+      <c r="CQ4">
+        <v>963</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>108</v>
+      </c>
+      <c r="CS4">
+        <v>1000</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>109</v>
+      </c>
+      <c r="CV4">
+        <v>1200</v>
+      </c>
+      <c r="CW4" t="s">
+        <v>110</v>
+      </c>
+      <c r="CX4">
+        <v>1600</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>111</v>
+      </c>
+      <c r="DA4">
+        <v>1800</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>112</v>
+      </c>
+      <c r="DC4">
+        <v>2000</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>113</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>48</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>49</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>34</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>12</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>43</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>51</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>52</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>25</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>1</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>16</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>55</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>38</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>24</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>42</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>35</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>26</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>27</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>6</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>24</v>
+      </c>
+      <c r="CV5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CX5" t="s">
+        <v>44</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>3</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:109" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786EF700-CF6F-D54A-9E69-BF04D951AC1D}">
-  <dimension ref="A2:F66"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="2" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
@@ -600,6 +2705,9 @@
       <c r="C2" s="1">
         <v>151</v>
       </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
@@ -613,6 +2721,9 @@
       <c r="C3" s="1">
         <v>150</v>
       </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
@@ -626,6 +2737,9 @@
       <c r="C4" s="1">
         <v>400</v>
       </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
@@ -640,7 +2754,9 @@
         <v>200</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -652,7 +2768,9 @@
       <c r="C6" s="1">
         <v>200</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -666,7 +2784,9 @@
         <v>200</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -679,7 +2799,9 @@
         <v>325</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -692,7 +2814,9 @@
         <v>1000</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -704,7 +2828,9 @@
       <c r="C10" s="1">
         <v>170</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
@@ -718,7 +2844,9 @@
       <c r="C11" s="1">
         <v>300</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
@@ -733,7 +2861,9 @@
         <v>239</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -746,7 +2876,9 @@
       <c r="C13" s="1">
         <v>479</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -760,7 +2892,9 @@
         <v>339</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -774,7 +2908,9 @@
         <v>349</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -787,7 +2923,9 @@
       <c r="C16" s="1">
         <v>2000</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -800,7 +2938,9 @@
       <c r="C17" s="1">
         <v>286</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -813,6 +2953,9 @@
       <c r="C18" s="1">
         <v>21</v>
       </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -824,6 +2967,9 @@
       <c r="C19" s="1">
         <v>39</v>
       </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -835,6 +2981,9 @@
       <c r="C20" s="1">
         <v>407</v>
       </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -846,6 +2995,9 @@
       <c r="C21" s="1">
         <v>154</v>
       </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -857,6 +3009,9 @@
       <c r="C22" s="1">
         <v>141</v>
       </c>
+      <c r="E22" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -868,6 +3023,9 @@
       <c r="C23" s="1">
         <v>233</v>
       </c>
+      <c r="E23" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -879,6 +3037,9 @@
       <c r="C24" s="1">
         <v>52</v>
       </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -890,6 +3051,9 @@
       <c r="C25" s="1">
         <v>34</v>
       </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -903,7 +3067,9 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -917,7 +3083,9 @@
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -931,7 +3099,9 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -943,7 +3113,9 @@
       <c r="C29" s="1">
         <v>1000</v>
       </c>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -956,7 +3128,9 @@
       <c r="C30" s="1">
         <v>400</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
@@ -971,7 +3145,9 @@
         <v>1600</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -983,7 +3159,9 @@
       <c r="C32" s="1">
         <v>836</v>
       </c>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -996,7 +3174,9 @@
       <c r="C33" s="1">
         <v>963</v>
       </c>
-      <c r="E33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1009,7 +3189,9 @@
       <c r="C34" s="1">
         <v>2000</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1022,7 +3204,9 @@
       <c r="C35" s="1">
         <v>168</v>
       </c>
-      <c r="E35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1035,6 +3219,9 @@
       <c r="C36" s="1">
         <v>150</v>
       </c>
+      <c r="D36" t="s">
+        <v>57</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
@@ -1048,7 +3235,9 @@
       <c r="C37" s="1">
         <v>200</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
@@ -1062,6 +3251,9 @@
       <c r="C38" s="1">
         <v>100</v>
       </c>
+      <c r="D38" t="s">
+        <v>57</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
@@ -1076,7 +3268,9 @@
         <v>70</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1088,8 +3282,13 @@
       <c r="C40" s="1">
         <v>100</v>
       </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1115,6 +3314,9 @@
       <c r="C42" s="1">
         <v>235</v>
       </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
@@ -1129,7 +3331,9 @@
         <v>350</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1143,7 +3347,9 @@
         <v>597</v>
       </c>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -1155,6 +3361,9 @@
       <c r="C45" s="1">
         <v>50</v>
       </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -1166,6 +3375,9 @@
       <c r="C46" s="1">
         <v>36</v>
       </c>
+      <c r="F46" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -1177,6 +3389,9 @@
       <c r="C47" s="1">
         <v>512</v>
       </c>
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -1188,6 +3403,9 @@
       <c r="C48" s="1">
         <v>108</v>
       </c>
+      <c r="D48" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -1199,6 +3417,9 @@
       <c r="C49" s="1">
         <v>562</v>
       </c>
+      <c r="D49" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -1210,6 +3431,9 @@
       <c r="C50" s="1">
         <v>64</v>
       </c>
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -1221,6 +3445,9 @@
       <c r="C51" s="1">
         <v>1600</v>
       </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
     </row>
@@ -1234,7 +3461,9 @@
       <c r="C52" s="1">
         <v>531</v>
       </c>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1248,7 +3477,9 @@
         <v>300</v>
       </c>
       <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1261,7 +3492,9 @@
       <c r="C54" s="1">
         <v>1800</v>
       </c>
-      <c r="E54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1275,7 +3508,9 @@
         <v>300</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -1287,7 +3522,9 @@
       <c r="C56" s="1">
         <v>276</v>
       </c>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1300,7 +3537,9 @@
       <c r="C57" s="1">
         <v>345</v>
       </c>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1313,7 +3552,9 @@
       <c r="C58" s="1">
         <v>300</v>
       </c>
-      <c r="E58" s="1"/>
+      <c r="E58" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1326,7 +3567,9 @@
       <c r="C59" s="1">
         <v>300</v>
       </c>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1340,7 +3583,9 @@
         <v>350</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -1354,7 +3599,9 @@
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -1366,7 +3613,9 @@
       <c r="C62" s="1">
         <v>350</v>
       </c>
-      <c r="E62" s="1"/>
+      <c r="E62" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1379,7 +3628,9 @@
       <c r="C63" s="1">
         <v>2000</v>
       </c>
-      <c r="D63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -1392,8 +3643,11 @@
       <c r="C64" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="22" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>56</v>
       </c>
@@ -1403,8 +3657,11 @@
       <c r="C65" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="22" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>56</v>
       </c>
@@ -1413,6 +3670,9 @@
       </c>
       <c r="C66" s="1">
         <v>430</v>
+      </c>
+      <c r="D66" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
